--- a/api/fixtures/digital-consent-import.xlsx
+++ b/api/fixtures/digital-consent-import.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TS01900</t>
+          <t>EMPAPI-CONSENT-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TS01901</t>
+          <t>EMPAPI-CONSENT-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TS01902</t>
+          <t>EMPAPI-CONSENT-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TS01903</t>
+          <t>EMPAPI-CONSENT-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
